--- a/output/reports/cv_experiment_NaiveBayes_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_NaiveBayes_kmeans_classification.xlsx
@@ -491,19 +491,19 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.04170870780944824</v>
+        <v>0.06928181648254395</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9159194082051126</v>
+        <v>0.8345842018580316</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9220779220779221</v>
+        <v>0.8961038961038961</v>
       </c>
       <c r="G2" t="n">
-        <v>0.8969508086253368</v>
+        <v>0.8472292264440773</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9880109068420757</v>
+        <v>0.9847360431776017</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -526,19 +526,19 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.04834914207458496</v>
+        <v>0.03646707534790039</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9177548235305235</v>
+        <v>0.8402780798375249</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9220779220779221</v>
+        <v>0.8961038961038961</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8969508086253368</v>
+        <v>0.8472292264440773</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9880109068420757</v>
+        <v>0.9847360431776017</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -622,19 +622,19 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.04170870780944824</v>
+        <v>0.06928181648254395</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9159194082051126</v>
+        <v>0.8345842018580316</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9220779220779221</v>
+        <v>0.8961038961038961</v>
       </c>
       <c r="G2" t="n">
-        <v>0.8969508086253368</v>
+        <v>0.8472292264440773</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9880109068420757</v>
+        <v>0.9847360431776017</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -657,19 +657,19 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.04834914207458496</v>
+        <v>0.03646707534790039</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9177548235305235</v>
+        <v>0.8402780798375249</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9220779220779221</v>
+        <v>0.8961038961038961</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8969508086253368</v>
+        <v>0.8472292264440773</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9880109068420757</v>
+        <v>0.9847360431776017</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>

--- a/output/reports/cv_experiment_NaiveBayes_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_NaiveBayes_kmeans_classification.xlsx
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.06928181648254395</v>
+        <v>0.02515745162963867</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8345842018580316</v>
+        <v>0.9804397703729418</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8961038961038961</v>
+        <v>0.987012987012987</v>
       </c>
       <c r="G2" t="n">
-        <v>0.8472292264440773</v>
+        <v>0.986977845425334</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9847360431776017</v>
+        <v>0.9863175675675676</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'priors': None, 'var_smoothing': 0.0001}</t>
+          <t>{'priors': None, 'var_smoothing': 1e-11}</t>
         </is>
       </c>
     </row>
@@ -526,23 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.03646707534790039</v>
+        <v>0.0369257926940918</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8402780798375249</v>
+        <v>0.9804280526546304</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8961038961038961</v>
+        <v>0.987012987012987</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8472292264440773</v>
+        <v>0.986977845425334</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9847360431776017</v>
+        <v>0.9863175675675676</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'priors': None, 'var_smoothing': 0.0001}</t>
+          <t>{'priors': None, 'var_smoothing': 1e-11}</t>
         </is>
       </c>
     </row>
@@ -622,23 +622,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.06928181648254395</v>
+        <v>0.02515745162963867</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8345842018580316</v>
+        <v>0.9804397703729418</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8961038961038961</v>
+        <v>0.987012987012987</v>
       </c>
       <c r="G2" t="n">
-        <v>0.8472292264440773</v>
+        <v>0.986977845425334</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9847360431776017</v>
+        <v>0.9863175675675676</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'priors': None, 'var_smoothing': 0.0001}</t>
+          <t>{'priors': None, 'var_smoothing': 1e-11}</t>
         </is>
       </c>
     </row>
@@ -657,23 +657,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.03646707534790039</v>
+        <v>0.0369257926940918</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8402780798375249</v>
+        <v>0.9804280526546304</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8961038961038961</v>
+        <v>0.987012987012987</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8472292264440773</v>
+        <v>0.986977845425334</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9847360431776017</v>
+        <v>0.9863175675675676</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'priors': None, 'var_smoothing': 0.0001}</t>
+          <t>{'priors': None, 'var_smoothing': 1e-11}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_NaiveBayes_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_NaiveBayes_kmeans_classification.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.02515745162963867</v>
+        <v>0.05123615264892578</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9804397703729418</v>
+        <v>0.7094700697920722</v>
       </c>
       <c r="F2" t="n">
-        <v>0.987012987012987</v>
+        <v>0.6938775510204082</v>
       </c>
       <c r="G2" t="n">
-        <v>0.986977845425334</v>
+        <v>0.6762950279046169</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9863175675675676</v>
+        <v>0.921294368087371</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'priors': None, 'var_smoothing': 1e-11}</t>
+          <t>{'priors': None, 'var_smoothing': 0.0001}</t>
         </is>
       </c>
     </row>
@@ -526,23 +526,58 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0369257926940918</v>
+        <v>0.03654861450195312</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9804280526546304</v>
+        <v>0.714517068021572</v>
       </c>
       <c r="F3" t="n">
-        <v>0.987012987012987</v>
+        <v>0.6938775510204082</v>
       </c>
       <c r="G3" t="n">
-        <v>0.986977845425334</v>
+        <v>0.6762950279046169</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9863175675675676</v>
+        <v>0.921294368087371</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'priors': None, 'var_smoothing': 1e-11}</t>
+          <t>{'priors': None, 'var_smoothing': 0.0001}</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>NaiveBayes</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.04615664482116699</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.7147236071909463</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.6938775510204082</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.6762950279046169</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.921294368087371</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>{'priors': None, 'var_smoothing': 0.0001}</t>
         </is>
       </c>
     </row>
@@ -557,7 +592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -622,23 +657,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.02515745162963867</v>
+        <v>0.05123615264892578</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9804397703729418</v>
+        <v>0.7094700697920722</v>
       </c>
       <c r="F2" t="n">
-        <v>0.987012987012987</v>
+        <v>0.6938775510204082</v>
       </c>
       <c r="G2" t="n">
-        <v>0.986977845425334</v>
+        <v>0.6762950279046169</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9863175675675676</v>
+        <v>0.921294368087371</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'priors': None, 'var_smoothing': 1e-11}</t>
+          <t>{'priors': None, 'var_smoothing': 0.0001}</t>
         </is>
       </c>
     </row>
@@ -657,23 +692,58 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0369257926940918</v>
+        <v>0.03654861450195312</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9804280526546304</v>
+        <v>0.714517068021572</v>
       </c>
       <c r="F3" t="n">
-        <v>0.987012987012987</v>
+        <v>0.6938775510204082</v>
       </c>
       <c r="G3" t="n">
-        <v>0.986977845425334</v>
+        <v>0.6762950279046169</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9863175675675676</v>
+        <v>0.921294368087371</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'priors': None, 'var_smoothing': 1e-11}</t>
+          <t>{'priors': None, 'var_smoothing': 0.0001}</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>NaiveBayes</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.04615664482116699</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.7147236071909463</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.6938775510204082</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.6762950279046169</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.921294368087371</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>{'priors': None, 'var_smoothing': 0.0001}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_NaiveBayes_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_NaiveBayes_kmeans_classification.xlsx
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.05123615264892578</v>
+        <v>0.2130286693572998</v>
       </c>
       <c r="E2" t="n">
-        <v>0.7094700697920722</v>
+        <v>0.758522079737817</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6938775510204082</v>
+        <v>0.8201956271576525</v>
       </c>
       <c r="G2" t="n">
-        <v>0.6762950279046169</v>
+        <v>0.7654782974318119</v>
       </c>
       <c r="H2" t="n">
-        <v>0.921294368087371</v>
+        <v>0.8779147698533132</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'priors': None, 'var_smoothing': 0.0001}</t>
+          <t>{'priors': None, 'var_smoothing': 1e-11}</t>
         </is>
       </c>
     </row>
@@ -526,23 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.03654861450195312</v>
+        <v>0.1723580360412598</v>
       </c>
       <c r="E3" t="n">
-        <v>0.714517068021572</v>
+        <v>0.7588098200722057</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6938775510204082</v>
+        <v>0.8201956271576525</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6762950279046169</v>
+        <v>0.7654782974318119</v>
       </c>
       <c r="H3" t="n">
-        <v>0.921294368087371</v>
+        <v>0.8779147698533132</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'priors': None, 'var_smoothing': 0.0001}</t>
+          <t>{'priors': None, 'var_smoothing': 1e-11}</t>
         </is>
       </c>
     </row>
@@ -561,23 +561,23 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>0.04615664482116699</v>
+        <v>0.2233843803405762</v>
       </c>
       <c r="E4" t="n">
-        <v>0.7147236071909463</v>
+        <v>0.7592605161401397</v>
       </c>
       <c r="F4" t="n">
-        <v>0.6938775510204082</v>
+        <v>0.8201956271576525</v>
       </c>
       <c r="G4" t="n">
-        <v>0.6762950279046169</v>
+        <v>0.7654782974318119</v>
       </c>
       <c r="H4" t="n">
-        <v>0.921294368087371</v>
+        <v>0.8779147698533132</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>{'priors': None, 'var_smoothing': 0.0001}</t>
+          <t>{'priors': None, 'var_smoothing': 1e-11}</t>
         </is>
       </c>
     </row>
@@ -657,23 +657,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.05123615264892578</v>
+        <v>0.2130286693572998</v>
       </c>
       <c r="E2" t="n">
-        <v>0.7094700697920722</v>
+        <v>0.758522079737817</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6938775510204082</v>
+        <v>0.8201956271576525</v>
       </c>
       <c r="G2" t="n">
-        <v>0.6762950279046169</v>
+        <v>0.7654782974318119</v>
       </c>
       <c r="H2" t="n">
-        <v>0.921294368087371</v>
+        <v>0.8779147698533132</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'priors': None, 'var_smoothing': 0.0001}</t>
+          <t>{'priors': None, 'var_smoothing': 1e-11}</t>
         </is>
       </c>
     </row>
@@ -692,23 +692,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.03654861450195312</v>
+        <v>0.1723580360412598</v>
       </c>
       <c r="E3" t="n">
-        <v>0.714517068021572</v>
+        <v>0.7588098200722057</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6938775510204082</v>
+        <v>0.8201956271576525</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6762950279046169</v>
+        <v>0.7654782974318119</v>
       </c>
       <c r="H3" t="n">
-        <v>0.921294368087371</v>
+        <v>0.8779147698533132</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'priors': None, 'var_smoothing': 0.0001}</t>
+          <t>{'priors': None, 'var_smoothing': 1e-11}</t>
         </is>
       </c>
     </row>
@@ -727,23 +727,23 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>0.04615664482116699</v>
+        <v>0.2233843803405762</v>
       </c>
       <c r="E4" t="n">
-        <v>0.7147236071909463</v>
+        <v>0.7592605161401397</v>
       </c>
       <c r="F4" t="n">
-        <v>0.6938775510204082</v>
+        <v>0.8201956271576525</v>
       </c>
       <c r="G4" t="n">
-        <v>0.6762950279046169</v>
+        <v>0.7654782974318119</v>
       </c>
       <c r="H4" t="n">
-        <v>0.921294368087371</v>
+        <v>0.8779147698533132</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>{'priors': None, 'var_smoothing': 0.0001}</t>
+          <t>{'priors': None, 'var_smoothing': 1e-11}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_NaiveBayes_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_NaiveBayes_kmeans_classification.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,19 +491,19 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2130286693572998</v>
+        <v>0.03733372688293457</v>
       </c>
       <c r="E2" t="n">
-        <v>0.758522079737817</v>
+        <v>0.9804397703729418</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8201956271576525</v>
+        <v>0.987012987012987</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7654782974318119</v>
+        <v>0.986977845425334</v>
       </c>
       <c r="H2" t="n">
-        <v>0.8779147698533132</v>
+        <v>0.9863175675675676</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -526,56 +526,21 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1723580360412598</v>
+        <v>0.03991031646728516</v>
       </c>
       <c r="E3" t="n">
-        <v>0.7588098200722057</v>
+        <v>0.9804280526546304</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8201956271576525</v>
+        <v>0.987012987012987</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7654782974318119</v>
+        <v>0.986977845425334</v>
       </c>
       <c r="H3" t="n">
-        <v>0.8779147698533132</v>
+        <v>0.9863175675675676</v>
       </c>
       <c r="I3" t="inlineStr">
-        <is>
-          <t>{'priors': None, 'var_smoothing': 1e-11}</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Classification</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>NaiveBayes</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>10</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0.2233843803405762</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.7592605161401397</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.8201956271576525</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0.7654782974318119</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.8779147698533132</v>
-      </c>
-      <c r="I4" t="inlineStr">
         <is>
           <t>{'priors': None, 'var_smoothing': 1e-11}</t>
         </is>
@@ -592,7 +557,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -657,19 +622,19 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2130286693572998</v>
+        <v>0.03733372688293457</v>
       </c>
       <c r="E2" t="n">
-        <v>0.758522079737817</v>
+        <v>0.9804397703729418</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8201956271576525</v>
+        <v>0.987012987012987</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7654782974318119</v>
+        <v>0.986977845425334</v>
       </c>
       <c r="H2" t="n">
-        <v>0.8779147698533132</v>
+        <v>0.9863175675675676</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -692,56 +657,21 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1723580360412598</v>
+        <v>0.03991031646728516</v>
       </c>
       <c r="E3" t="n">
-        <v>0.7588098200722057</v>
+        <v>0.9804280526546304</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8201956271576525</v>
+        <v>0.987012987012987</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7654782974318119</v>
+        <v>0.986977845425334</v>
       </c>
       <c r="H3" t="n">
-        <v>0.8779147698533132</v>
+        <v>0.9863175675675676</v>
       </c>
       <c r="I3" t="inlineStr">
-        <is>
-          <t>{'priors': None, 'var_smoothing': 1e-11}</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Classification</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>NaiveBayes</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>10</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0.2233843803405762</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.7592605161401397</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.8201956271576525</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0.7654782974318119</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.8779147698533132</v>
-      </c>
-      <c r="I4" t="inlineStr">
         <is>
           <t>{'priors': None, 'var_smoothing': 1e-11}</t>
         </is>

--- a/output/reports/cv_experiment_NaiveBayes_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_NaiveBayes_kmeans_classification.xlsx
@@ -491,7 +491,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.03733372688293457</v>
+        <v>0.03755855560302734</v>
       </c>
       <c r="E2" t="n">
         <v>0.9804397703729418</v>
@@ -526,7 +526,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.03991031646728516</v>
+        <v>0.03737854957580566</v>
       </c>
       <c r="E3" t="n">
         <v>0.9804280526546304</v>
@@ -622,7 +622,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.03733372688293457</v>
+        <v>0.03755855560302734</v>
       </c>
       <c r="E2" t="n">
         <v>0.9804397703729418</v>
@@ -657,7 +657,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.03991031646728516</v>
+        <v>0.03737854957580566</v>
       </c>
       <c r="E3" t="n">
         <v>0.9804280526546304</v>

--- a/output/reports/cv_experiment_NaiveBayes_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_NaiveBayes_kmeans_classification.xlsx
@@ -491,7 +491,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.03755855560302734</v>
+        <v>0.02928304672241211</v>
       </c>
       <c r="E2" t="n">
         <v>0.9804397703729418</v>
@@ -526,7 +526,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.03737854957580566</v>
+        <v>0.03797769546508789</v>
       </c>
       <c r="E3" t="n">
         <v>0.9804280526546304</v>
@@ -622,7 +622,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.03755855560302734</v>
+        <v>0.02928304672241211</v>
       </c>
       <c r="E2" t="n">
         <v>0.9804397703729418</v>
@@ -657,7 +657,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.03737854957580566</v>
+        <v>0.03797769546508789</v>
       </c>
       <c r="E3" t="n">
         <v>0.9804280526546304</v>

--- a/output/reports/cv_experiment_NaiveBayes_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_NaiveBayes_kmeans_classification.xlsx
@@ -491,7 +491,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.02928304672241211</v>
+        <v>0.02556300163269043</v>
       </c>
       <c r="E2" t="n">
         <v>0.9804397703729418</v>
@@ -507,7 +507,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'priors': None, 'var_smoothing': 1e-11}</t>
+          <t>{'var_smoothing': 1e-11, 'priors': None}</t>
         </is>
       </c>
     </row>
@@ -526,7 +526,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.03797769546508789</v>
+        <v>0.03720545768737793</v>
       </c>
       <c r="E3" t="n">
         <v>0.9804280526546304</v>
@@ -542,7 +542,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'priors': None, 'var_smoothing': 1e-11}</t>
+          <t>{'var_smoothing': 1e-11, 'priors': None}</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.02928304672241211</v>
+        <v>0.02556300163269043</v>
       </c>
       <c r="E2" t="n">
         <v>0.9804397703729418</v>
@@ -638,7 +638,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'priors': None, 'var_smoothing': 1e-11}</t>
+          <t>{'var_smoothing': 1e-11, 'priors': None}</t>
         </is>
       </c>
     </row>
@@ -657,7 +657,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.03797769546508789</v>
+        <v>0.03720545768737793</v>
       </c>
       <c r="E3" t="n">
         <v>0.9804280526546304</v>
@@ -673,7 +673,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'priors': None, 'var_smoothing': 1e-11}</t>
+          <t>{'var_smoothing': 1e-11, 'priors': None}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_NaiveBayes_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_NaiveBayes_kmeans_classification.xlsx
@@ -491,19 +491,19 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.02556300163269043</v>
+        <v>0.2610046863555908</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9804397703729418</v>
+        <v>0.758522079737817</v>
       </c>
       <c r="F2" t="n">
-        <v>0.987012987012987</v>
+        <v>0.8201956271576525</v>
       </c>
       <c r="G2" t="n">
-        <v>0.986977845425334</v>
+        <v>0.7654782974318119</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9863175675675676</v>
+        <v>0.8779147698533132</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -526,19 +526,19 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.03720545768737793</v>
+        <v>0.1970951557159424</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9804280526546304</v>
+        <v>0.7588098200722057</v>
       </c>
       <c r="F3" t="n">
-        <v>0.987012987012987</v>
+        <v>0.8201956271576525</v>
       </c>
       <c r="G3" t="n">
-        <v>0.986977845425334</v>
+        <v>0.7654782974318119</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9863175675675676</v>
+        <v>0.8779147698533132</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -622,19 +622,19 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.02556300163269043</v>
+        <v>0.2610046863555908</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9804397703729418</v>
+        <v>0.758522079737817</v>
       </c>
       <c r="F2" t="n">
-        <v>0.987012987012987</v>
+        <v>0.8201956271576525</v>
       </c>
       <c r="G2" t="n">
-        <v>0.986977845425334</v>
+        <v>0.7654782974318119</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9863175675675676</v>
+        <v>0.8779147698533132</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -657,19 +657,19 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.03720545768737793</v>
+        <v>0.1970951557159424</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9804280526546304</v>
+        <v>0.7588098200722057</v>
       </c>
       <c r="F3" t="n">
-        <v>0.987012987012987</v>
+        <v>0.8201956271576525</v>
       </c>
       <c r="G3" t="n">
-        <v>0.986977845425334</v>
+        <v>0.7654782974318119</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9863175675675676</v>
+        <v>0.8779147698533132</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>

--- a/output/reports/cv_experiment_NaiveBayes_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_NaiveBayes_kmeans_classification.xlsx
@@ -488,22 +488,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2610046863555908</v>
+        <v>0.1194067001342773</v>
       </c>
       <c r="E2" t="n">
-        <v>0.758522079737817</v>
+        <v>0.3295822460801396</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8201956271576525</v>
+        <v>0.546875</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7654782974318119</v>
+        <v>0.310129522979618</v>
       </c>
       <c r="H2" t="n">
-        <v>0.8779147698533132</v>
+        <v>0.875607421875</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -523,22 +523,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1970951557159424</v>
+        <v>0.09002304077148438</v>
       </c>
       <c r="E3" t="n">
-        <v>0.7588098200722057</v>
+        <v>0.3414151215023095</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8201956271576525</v>
+        <v>0.546875</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7654782974318119</v>
+        <v>0.310129522979618</v>
       </c>
       <c r="H3" t="n">
-        <v>0.8779147698533132</v>
+        <v>0.875607421875</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -619,22 +619,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2610046863555908</v>
+        <v>0.1194067001342773</v>
       </c>
       <c r="E2" t="n">
-        <v>0.758522079737817</v>
+        <v>0.3295822460801396</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8201956271576525</v>
+        <v>0.546875</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7654782974318119</v>
+        <v>0.310129522979618</v>
       </c>
       <c r="H2" t="n">
-        <v>0.8779147698533132</v>
+        <v>0.875607421875</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -654,22 +654,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1970951557159424</v>
+        <v>0.09002304077148438</v>
       </c>
       <c r="E3" t="n">
-        <v>0.7588098200722057</v>
+        <v>0.3414151215023095</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8201956271576525</v>
+        <v>0.546875</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7654782974318119</v>
+        <v>0.310129522979618</v>
       </c>
       <c r="H3" t="n">
-        <v>0.8779147698533132</v>
+        <v>0.875607421875</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>

--- a/output/reports/cv_experiment_NaiveBayes_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_NaiveBayes_kmeans_classification.xlsx
@@ -488,22 +488,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1194067001342773</v>
+        <v>0.221412181854248</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3295822460801396</v>
+        <v>0.5534276352203948</v>
       </c>
       <c r="F2" t="n">
-        <v>0.546875</v>
+        <v>0.8697745122878136</v>
       </c>
       <c r="G2" t="n">
-        <v>0.310129522979618</v>
+        <v>0.5553941137590488</v>
       </c>
       <c r="H2" t="n">
-        <v>0.875607421875</v>
+        <v>0.6969482505262322</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -523,22 +523,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.09002304077148438</v>
+        <v>0.2061653137207031</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3414151215023095</v>
+        <v>0.5584974950698796</v>
       </c>
       <c r="F3" t="n">
-        <v>0.546875</v>
+        <v>0.8697745122878136</v>
       </c>
       <c r="G3" t="n">
-        <v>0.310129522979618</v>
+        <v>0.5553941137590488</v>
       </c>
       <c r="H3" t="n">
-        <v>0.875607421875</v>
+        <v>0.6969482505262322</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -619,22 +619,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1194067001342773</v>
+        <v>0.221412181854248</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3295822460801396</v>
+        <v>0.5534276352203948</v>
       </c>
       <c r="F2" t="n">
-        <v>0.546875</v>
+        <v>0.8697745122878136</v>
       </c>
       <c r="G2" t="n">
-        <v>0.310129522979618</v>
+        <v>0.5553941137590488</v>
       </c>
       <c r="H2" t="n">
-        <v>0.875607421875</v>
+        <v>0.6969482505262322</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -654,22 +654,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.09002304077148438</v>
+        <v>0.2061653137207031</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3414151215023095</v>
+        <v>0.5584974950698796</v>
       </c>
       <c r="F3" t="n">
-        <v>0.546875</v>
+        <v>0.8697745122878136</v>
       </c>
       <c r="G3" t="n">
-        <v>0.310129522979618</v>
+        <v>0.5553941137590488</v>
       </c>
       <c r="H3" t="n">
-        <v>0.875607421875</v>
+        <v>0.6969482505262322</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>

--- a/output/reports/cv_experiment_NaiveBayes_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_NaiveBayes_kmeans_classification.xlsx
@@ -491,19 +491,19 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.221412181854248</v>
+        <v>0.02712750434875488</v>
       </c>
       <c r="E2" t="n">
-        <v>0.5534276352203948</v>
+        <v>0.9804397703729418</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8697745122878136</v>
+        <v>0.987012987012987</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5553941137590488</v>
+        <v>0.986977845425334</v>
       </c>
       <c r="H2" t="n">
-        <v>0.6969482505262322</v>
+        <v>0.9863175675675676</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -526,19 +526,19 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.2061653137207031</v>
+        <v>0.02701616287231445</v>
       </c>
       <c r="E3" t="n">
-        <v>0.5584974950698796</v>
+        <v>0.9804280526546304</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8697745122878136</v>
+        <v>0.987012987012987</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5553941137590488</v>
+        <v>0.986977845425334</v>
       </c>
       <c r="H3" t="n">
-        <v>0.6969482505262322</v>
+        <v>0.9863175675675676</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -622,19 +622,19 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.221412181854248</v>
+        <v>0.02712750434875488</v>
       </c>
       <c r="E2" t="n">
-        <v>0.5534276352203948</v>
+        <v>0.9804397703729418</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8697745122878136</v>
+        <v>0.987012987012987</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5553941137590488</v>
+        <v>0.986977845425334</v>
       </c>
       <c r="H2" t="n">
-        <v>0.6969482505262322</v>
+        <v>0.9863175675675676</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -657,19 +657,19 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.2061653137207031</v>
+        <v>0.02701616287231445</v>
       </c>
       <c r="E3" t="n">
-        <v>0.5584974950698796</v>
+        <v>0.9804280526546304</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8697745122878136</v>
+        <v>0.987012987012987</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5553941137590488</v>
+        <v>0.986977845425334</v>
       </c>
       <c r="H3" t="n">
-        <v>0.6969482505262322</v>
+        <v>0.9863175675675676</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>

--- a/output/reports/cv_experiment_NaiveBayes_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_NaiveBayes_kmeans_classification.xlsx
@@ -491,7 +491,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.02712750434875488</v>
+        <v>0.02542209625244141</v>
       </c>
       <c r="E2" t="n">
         <v>0.9804397703729418</v>
@@ -526,7 +526,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.02701616287231445</v>
+        <v>0.03789854049682617</v>
       </c>
       <c r="E3" t="n">
         <v>0.9804280526546304</v>
@@ -622,7 +622,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.02712750434875488</v>
+        <v>0.02542209625244141</v>
       </c>
       <c r="E2" t="n">
         <v>0.9804397703729418</v>
@@ -657,7 +657,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.02701616287231445</v>
+        <v>0.03789854049682617</v>
       </c>
       <c r="E3" t="n">
         <v>0.9804280526546304</v>

--- a/output/reports/cv_experiment_NaiveBayes_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_NaiveBayes_kmeans_classification.xlsx
@@ -491,7 +491,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.02542209625244141</v>
+        <v>0.03090858459472656</v>
       </c>
       <c r="E2" t="n">
         <v>0.9804397703729418</v>
@@ -526,7 +526,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.03789854049682617</v>
+        <v>0.03694772720336914</v>
       </c>
       <c r="E3" t="n">
         <v>0.9804280526546304</v>
@@ -622,7 +622,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.02542209625244141</v>
+        <v>0.03090858459472656</v>
       </c>
       <c r="E2" t="n">
         <v>0.9804397703729418</v>
@@ -657,7 +657,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.03789854049682617</v>
+        <v>0.03694772720336914</v>
       </c>
       <c r="E3" t="n">
         <v>0.9804280526546304</v>

--- a/output/reports/cv_experiment_NaiveBayes_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_NaiveBayes_kmeans_classification.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,7 +491,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.03090858459472656</v>
+        <v>0.05379128456115723</v>
       </c>
       <c r="E2" t="n">
         <v>0.9804397703729418</v>
@@ -526,7 +526,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.03694772720336914</v>
+        <v>0.08011054992675781</v>
       </c>
       <c r="E3" t="n">
         <v>0.9804280526546304</v>
@@ -541,6 +541,41 @@
         <v>0.9863175675675676</v>
       </c>
       <c r="I3" t="inlineStr">
+        <is>
+          <t>{'var_smoothing': 1e-11, 'priors': None}</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>NaiveBayes</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.06212043762207031</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.9804441893856517</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.987012987012987</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.986977845425334</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.9863175675675676</v>
+      </c>
+      <c r="I4" t="inlineStr">
         <is>
           <t>{'var_smoothing': 1e-11, 'priors': None}</t>
         </is>
@@ -557,7 +592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -622,7 +657,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.03090858459472656</v>
+        <v>0.05379128456115723</v>
       </c>
       <c r="E2" t="n">
         <v>0.9804397703729418</v>
@@ -657,7 +692,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.03694772720336914</v>
+        <v>0.08011054992675781</v>
       </c>
       <c r="E3" t="n">
         <v>0.9804280526546304</v>
@@ -672,6 +707,41 @@
         <v>0.9863175675675676</v>
       </c>
       <c r="I3" t="inlineStr">
+        <is>
+          <t>{'var_smoothing': 1e-11, 'priors': None}</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>NaiveBayes</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.06212043762207031</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.9804441893856517</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.987012987012987</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.986977845425334</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.9863175675675676</v>
+      </c>
+      <c r="I4" t="inlineStr">
         <is>
           <t>{'var_smoothing': 1e-11, 'priors': None}</t>
         </is>

--- a/output/reports/cv_experiment_NaiveBayes_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_NaiveBayes_kmeans_classification.xlsx
@@ -491,7 +491,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.05379128456115723</v>
+        <v>0.03718662261962891</v>
       </c>
       <c r="E2" t="n">
         <v>0.9804397703729418</v>
@@ -526,7 +526,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.08011054992675781</v>
+        <v>0.06055116653442383</v>
       </c>
       <c r="E3" t="n">
         <v>0.9804280526546304</v>
@@ -561,7 +561,7 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>0.06212043762207031</v>
+        <v>0.06001806259155273</v>
       </c>
       <c r="E4" t="n">
         <v>0.9804441893856517</v>
@@ -657,7 +657,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.05379128456115723</v>
+        <v>0.03718662261962891</v>
       </c>
       <c r="E2" t="n">
         <v>0.9804397703729418</v>
@@ -692,7 +692,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.08011054992675781</v>
+        <v>0.06055116653442383</v>
       </c>
       <c r="E3" t="n">
         <v>0.9804280526546304</v>
@@ -727,7 +727,7 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>0.06212043762207031</v>
+        <v>0.06001806259155273</v>
       </c>
       <c r="E4" t="n">
         <v>0.9804441893856517</v>

--- a/output/reports/cv_experiment_NaiveBayes_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_NaiveBayes_kmeans_classification.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,19 +491,19 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.03718662261962891</v>
+        <v>0.1501247882843018</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9804397703729418</v>
+        <v>0.758522079737817</v>
       </c>
       <c r="F2" t="n">
-        <v>0.987012987012987</v>
+        <v>0.8201956271576525</v>
       </c>
       <c r="G2" t="n">
-        <v>0.986977845425334</v>
+        <v>0.7654782974318119</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9863175675675676</v>
+        <v>0.8779147698533132</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -526,56 +526,21 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.06055116653442383</v>
+        <v>0.2186179161071777</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9804280526546304</v>
+        <v>0.7588098200722057</v>
       </c>
       <c r="F3" t="n">
-        <v>0.987012987012987</v>
+        <v>0.8201956271576525</v>
       </c>
       <c r="G3" t="n">
-        <v>0.986977845425334</v>
+        <v>0.7654782974318119</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9863175675675676</v>
+        <v>0.8779147698533132</v>
       </c>
       <c r="I3" t="inlineStr">
-        <is>
-          <t>{'var_smoothing': 1e-11, 'priors': None}</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Classification</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>NaiveBayes</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>10</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0.06001806259155273</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.9804441893856517</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.987012987012987</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0.986977845425334</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.9863175675675676</v>
-      </c>
-      <c r="I4" t="inlineStr">
         <is>
           <t>{'var_smoothing': 1e-11, 'priors': None}</t>
         </is>
@@ -592,7 +557,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -657,19 +622,19 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.03718662261962891</v>
+        <v>0.1501247882843018</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9804397703729418</v>
+        <v>0.758522079737817</v>
       </c>
       <c r="F2" t="n">
-        <v>0.987012987012987</v>
+        <v>0.8201956271576525</v>
       </c>
       <c r="G2" t="n">
-        <v>0.986977845425334</v>
+        <v>0.7654782974318119</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9863175675675676</v>
+        <v>0.8779147698533132</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -692,56 +657,21 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.06055116653442383</v>
+        <v>0.2186179161071777</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9804280526546304</v>
+        <v>0.7588098200722057</v>
       </c>
       <c r="F3" t="n">
-        <v>0.987012987012987</v>
+        <v>0.8201956271576525</v>
       </c>
       <c r="G3" t="n">
-        <v>0.986977845425334</v>
+        <v>0.7654782974318119</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9863175675675676</v>
+        <v>0.8779147698533132</v>
       </c>
       <c r="I3" t="inlineStr">
-        <is>
-          <t>{'var_smoothing': 1e-11, 'priors': None}</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Classification</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>NaiveBayes</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>10</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0.06001806259155273</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.9804441893856517</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.987012987012987</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0.986977845425334</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.9863175675675676</v>
-      </c>
-      <c r="I4" t="inlineStr">
         <is>
           <t>{'var_smoothing': 1e-11, 'priors': None}</t>
         </is>

--- a/output/reports/cv_experiment_NaiveBayes_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_NaiveBayes_kmeans_classification.xlsx
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1501247882843018</v>
+        <v>0.3706979751586914</v>
       </c>
       <c r="E2" t="n">
-        <v>0.758522079737817</v>
+        <v>0.8947909997695277</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8201956271576525</v>
+        <v>0.8950287698926961</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7654782974318119</v>
+        <v>0.8943395818247909</v>
       </c>
       <c r="H2" t="n">
-        <v>0.8779147698533132</v>
+        <v>0.9796068527587372</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'var_smoothing': 1e-11, 'priors': None}</t>
+          <t>{'var_smoothing': 1e-05, 'priors': None}</t>
         </is>
       </c>
     </row>
@@ -526,23 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.2186179161071777</v>
+        <v>0.4051382541656494</v>
       </c>
       <c r="E3" t="n">
-        <v>0.7588098200722057</v>
+        <v>0.8947778241987672</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8201956271576525</v>
+        <v>0.8950287698926961</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7654782974318119</v>
+        <v>0.8943395818247909</v>
       </c>
       <c r="H3" t="n">
-        <v>0.8779147698533132</v>
+        <v>0.9796039290947858</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'var_smoothing': 1e-11, 'priors': None}</t>
+          <t>{'var_smoothing': 0.0001, 'priors': None}</t>
         </is>
       </c>
     </row>
@@ -622,23 +622,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1501247882843018</v>
+        <v>0.3706979751586914</v>
       </c>
       <c r="E2" t="n">
-        <v>0.758522079737817</v>
+        <v>0.8947909997695277</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8201956271576525</v>
+        <v>0.8950287698926961</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7654782974318119</v>
+        <v>0.8943395818247909</v>
       </c>
       <c r="H2" t="n">
-        <v>0.8779147698533132</v>
+        <v>0.9796068527587372</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'var_smoothing': 1e-11, 'priors': None}</t>
+          <t>{'var_smoothing': 1e-05, 'priors': None}</t>
         </is>
       </c>
     </row>
@@ -657,23 +657,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.2186179161071777</v>
+        <v>0.4051382541656494</v>
       </c>
       <c r="E3" t="n">
-        <v>0.7588098200722057</v>
+        <v>0.8947778241987672</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8201956271576525</v>
+        <v>0.8950287698926961</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7654782974318119</v>
+        <v>0.8943395818247909</v>
       </c>
       <c r="H3" t="n">
-        <v>0.8779147698533132</v>
+        <v>0.9796039290947858</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'var_smoothing': 1e-11, 'priors': None}</t>
+          <t>{'var_smoothing': 0.0001, 'priors': None}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_NaiveBayes_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_NaiveBayes_kmeans_classification.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.3706979751586914</v>
+        <v>0.06044602394104004</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8947909997695277</v>
+        <v>0.9804397703729418</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8950287698926961</v>
+        <v>0.987012987012987</v>
       </c>
       <c r="G2" t="n">
-        <v>0.8943395818247909</v>
+        <v>0.986977845425334</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9796068527587372</v>
+        <v>0.9863175675675676</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'var_smoothing': 1e-05, 'priors': None}</t>
+          <t>{'var_smoothing': 1e-11, 'priors': None}</t>
         </is>
       </c>
     </row>
@@ -526,23 +526,58 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.4051382541656494</v>
+        <v>0.04830646514892578</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8947778241987672</v>
+        <v>0.9804280526546304</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8950287698926961</v>
+        <v>0.987012987012987</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8943395818247909</v>
+        <v>0.986977845425334</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9796039290947858</v>
+        <v>0.9863175675675676</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'var_smoothing': 0.0001, 'priors': None}</t>
+          <t>{'var_smoothing': 1e-11, 'priors': None}</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>NaiveBayes</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.07283878326416016</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.9804441893856517</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.987012987012987</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.986977845425334</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.9863175675675676</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>{'var_smoothing': 1e-11, 'priors': None}</t>
         </is>
       </c>
     </row>
@@ -557,7 +592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -622,23 +657,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.3706979751586914</v>
+        <v>0.06044602394104004</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8947909997695277</v>
+        <v>0.9804397703729418</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8950287698926961</v>
+        <v>0.987012987012987</v>
       </c>
       <c r="G2" t="n">
-        <v>0.8943395818247909</v>
+        <v>0.986977845425334</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9796068527587372</v>
+        <v>0.9863175675675676</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'var_smoothing': 1e-05, 'priors': None}</t>
+          <t>{'var_smoothing': 1e-11, 'priors': None}</t>
         </is>
       </c>
     </row>
@@ -657,23 +692,58 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.4051382541656494</v>
+        <v>0.04830646514892578</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8947778241987672</v>
+        <v>0.9804280526546304</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8950287698926961</v>
+        <v>0.987012987012987</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8943395818247909</v>
+        <v>0.986977845425334</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9796039290947858</v>
+        <v>0.9863175675675676</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'var_smoothing': 0.0001, 'priors': None}</t>
+          <t>{'var_smoothing': 1e-11, 'priors': None}</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>NaiveBayes</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.07283878326416016</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.9804441893856517</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.987012987012987</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.986977845425334</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.9863175675675676</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>{'var_smoothing': 1e-11, 'priors': None}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_NaiveBayes_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_NaiveBayes_kmeans_classification.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,19 +491,19 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.06044602394104004</v>
+        <v>0.1857089996337891</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9804397703729418</v>
+        <v>0.5534276352203948</v>
       </c>
       <c r="F2" t="n">
-        <v>0.987012987012987</v>
+        <v>0.8697745122878136</v>
       </c>
       <c r="G2" t="n">
-        <v>0.986977845425334</v>
+        <v>0.5553941137590488</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9863175675675676</v>
+        <v>0.6969482505262322</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -526,56 +526,21 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.04830646514892578</v>
+        <v>0.2213370800018311</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9804280526546304</v>
+        <v>0.5584974950698796</v>
       </c>
       <c r="F3" t="n">
-        <v>0.987012987012987</v>
+        <v>0.8697745122878136</v>
       </c>
       <c r="G3" t="n">
-        <v>0.986977845425334</v>
+        <v>0.5553941137590488</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9863175675675676</v>
+        <v>0.6969482505262322</v>
       </c>
       <c r="I3" t="inlineStr">
-        <is>
-          <t>{'var_smoothing': 1e-11, 'priors': None}</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Classification</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>NaiveBayes</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>10</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0.07283878326416016</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.9804441893856517</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.987012987012987</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0.986977845425334</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.9863175675675676</v>
-      </c>
-      <c r="I4" t="inlineStr">
         <is>
           <t>{'var_smoothing': 1e-11, 'priors': None}</t>
         </is>
@@ -592,7 +557,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -657,19 +622,19 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.06044602394104004</v>
+        <v>0.1857089996337891</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9804397703729418</v>
+        <v>0.5534276352203948</v>
       </c>
       <c r="F2" t="n">
-        <v>0.987012987012987</v>
+        <v>0.8697745122878136</v>
       </c>
       <c r="G2" t="n">
-        <v>0.986977845425334</v>
+        <v>0.5553941137590488</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9863175675675676</v>
+        <v>0.6969482505262322</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -692,56 +657,21 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.04830646514892578</v>
+        <v>0.2213370800018311</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9804280526546304</v>
+        <v>0.5584974950698796</v>
       </c>
       <c r="F3" t="n">
-        <v>0.987012987012987</v>
+        <v>0.8697745122878136</v>
       </c>
       <c r="G3" t="n">
-        <v>0.986977845425334</v>
+        <v>0.5553941137590488</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9863175675675676</v>
+        <v>0.6969482505262322</v>
       </c>
       <c r="I3" t="inlineStr">
-        <is>
-          <t>{'var_smoothing': 1e-11, 'priors': None}</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Classification</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>NaiveBayes</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>10</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0.07283878326416016</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.9804441893856517</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.987012987012987</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0.986977845425334</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.9863175675675676</v>
-      </c>
-      <c r="I4" t="inlineStr">
         <is>
           <t>{'var_smoothing': 1e-11, 'priors': None}</t>
         </is>

--- a/output/reports/cv_experiment_NaiveBayes_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_NaiveBayes_kmeans_classification.xlsx
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1857089996337891</v>
+        <v>0.3268022537231445</v>
       </c>
       <c r="E2" t="n">
-        <v>0.5534276352203948</v>
+        <v>0.79106389788666</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8697745122878136</v>
+        <v>0.8074300493769104</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5553941137590488</v>
+        <v>0.7975398631827457</v>
       </c>
       <c r="H2" t="n">
-        <v>0.6969482505262322</v>
+        <v>0.8671062626670155</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'var_smoothing': 1e-11, 'priors': None}</t>
+          <t>{'var_smoothing': 0.0001, 'priors': None}</t>
         </is>
       </c>
     </row>
@@ -526,19 +526,19 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.2213370800018311</v>
+        <v>0.4358818531036377</v>
       </c>
       <c r="E3" t="n">
-        <v>0.5584974950698796</v>
+        <v>0.7912015650524316</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8697745122878136</v>
+        <v>0.8074300493769104</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5553941137590488</v>
+        <v>0.7975398631827457</v>
       </c>
       <c r="H3" t="n">
-        <v>0.6969482505262322</v>
+        <v>0.8671067879968438</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -622,23 +622,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1857089996337891</v>
+        <v>0.3268022537231445</v>
       </c>
       <c r="E2" t="n">
-        <v>0.5534276352203948</v>
+        <v>0.79106389788666</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8697745122878136</v>
+        <v>0.8074300493769104</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5553941137590488</v>
+        <v>0.7975398631827457</v>
       </c>
       <c r="H2" t="n">
-        <v>0.6969482505262322</v>
+        <v>0.8671062626670155</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'var_smoothing': 1e-11, 'priors': None}</t>
+          <t>{'var_smoothing': 0.0001, 'priors': None}</t>
         </is>
       </c>
     </row>
@@ -657,19 +657,19 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.2213370800018311</v>
+        <v>0.4358818531036377</v>
       </c>
       <c r="E3" t="n">
-        <v>0.5584974950698796</v>
+        <v>0.7912015650524316</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8697745122878136</v>
+        <v>0.8074300493769104</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5553941137590488</v>
+        <v>0.7975398631827457</v>
       </c>
       <c r="H3" t="n">
-        <v>0.6969482505262322</v>
+        <v>0.8671067879968438</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>

--- a/output/reports/cv_experiment_NaiveBayes_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_NaiveBayes_kmeans_classification.xlsx
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.3268022537231445</v>
+        <v>0.0595390796661377</v>
       </c>
       <c r="E2" t="n">
-        <v>0.79106389788666</v>
+        <v>0.2583424476388876</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8074300493769104</v>
+        <v>0.4326530612244898</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7975398631827457</v>
+        <v>0.2576611820510127</v>
       </c>
       <c r="H2" t="n">
-        <v>0.8671062626670155</v>
+        <v>0.8504772317090102</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'var_smoothing': 0.0001, 'priors': None}</t>
+          <t>{'priors': None, 'var_smoothing': 1e-05}</t>
         </is>
       </c>
     </row>
@@ -526,23 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.4358818531036377</v>
+        <v>0.04764246940612793</v>
       </c>
       <c r="E3" t="n">
-        <v>0.7912015650524316</v>
+        <v>0.2529756910104267</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8074300493769104</v>
+        <v>0.4326530612244898</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7975398631827457</v>
+        <v>0.2576611820510127</v>
       </c>
       <c r="H3" t="n">
-        <v>0.8671067879968438</v>
+        <v>0.850476537553797</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'var_smoothing': 1e-11, 'priors': None}</t>
+          <t>{'priors': None, 'var_smoothing': 1e-11}</t>
         </is>
       </c>
     </row>
@@ -622,23 +622,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.3268022537231445</v>
+        <v>0.0595390796661377</v>
       </c>
       <c r="E2" t="n">
-        <v>0.79106389788666</v>
+        <v>0.2583424476388876</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8074300493769104</v>
+        <v>0.4326530612244898</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7975398631827457</v>
+        <v>0.2576611820510127</v>
       </c>
       <c r="H2" t="n">
-        <v>0.8671062626670155</v>
+        <v>0.8504772317090102</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'var_smoothing': 0.0001, 'priors': None}</t>
+          <t>{'priors': None, 'var_smoothing': 1e-05}</t>
         </is>
       </c>
     </row>
@@ -657,23 +657,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.4358818531036377</v>
+        <v>0.04764246940612793</v>
       </c>
       <c r="E3" t="n">
-        <v>0.7912015650524316</v>
+        <v>0.2529756910104267</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8074300493769104</v>
+        <v>0.4326530612244898</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7975398631827457</v>
+        <v>0.2576611820510127</v>
       </c>
       <c r="H3" t="n">
-        <v>0.8671067879968438</v>
+        <v>0.850476537553797</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'var_smoothing': 1e-11, 'priors': None}</t>
+          <t>{'priors': None, 'var_smoothing': 1e-11}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_NaiveBayes_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_NaiveBayes_kmeans_classification.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0595390796661377</v>
+        <v>0.05242013931274414</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2583424476388876</v>
+        <v>0.9804397703729418</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4326530612244898</v>
+        <v>0.987012987012987</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2576611820510127</v>
+        <v>0.986977845425334</v>
       </c>
       <c r="H2" t="n">
-        <v>0.8504772317090102</v>
+        <v>0.9863175675675676</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'priors': None, 'var_smoothing': 1e-05}</t>
+          <t>{'var_smoothing': 1e-11, 'priors': None}</t>
         </is>
       </c>
     </row>
@@ -526,23 +526,58 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.04764246940612793</v>
+        <v>0.04877781867980957</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2529756910104267</v>
+        <v>0.9804280526546304</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4326530612244898</v>
+        <v>0.987012987012987</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2576611820510127</v>
+        <v>0.986977845425334</v>
       </c>
       <c r="H3" t="n">
-        <v>0.850476537553797</v>
+        <v>0.9863175675675676</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'priors': None, 'var_smoothing': 1e-11}</t>
+          <t>{'var_smoothing': 1e-11, 'priors': None}</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>NaiveBayes</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.07150053977966309</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.9804441893856517</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.987012987012987</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.986977845425334</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.9863175675675676</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>{'var_smoothing': 1e-11, 'priors': None}</t>
         </is>
       </c>
     </row>
@@ -557,7 +592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -622,23 +657,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0595390796661377</v>
+        <v>0.05242013931274414</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2583424476388876</v>
+        <v>0.9804397703729418</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4326530612244898</v>
+        <v>0.987012987012987</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2576611820510127</v>
+        <v>0.986977845425334</v>
       </c>
       <c r="H2" t="n">
-        <v>0.8504772317090102</v>
+        <v>0.9863175675675676</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'priors': None, 'var_smoothing': 1e-05}</t>
+          <t>{'var_smoothing': 1e-11, 'priors': None}</t>
         </is>
       </c>
     </row>
@@ -657,23 +692,58 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.04764246940612793</v>
+        <v>0.04877781867980957</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2529756910104267</v>
+        <v>0.9804280526546304</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4326530612244898</v>
+        <v>0.987012987012987</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2576611820510127</v>
+        <v>0.986977845425334</v>
       </c>
       <c r="H3" t="n">
-        <v>0.850476537553797</v>
+        <v>0.9863175675675676</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'priors': None, 'var_smoothing': 1e-11}</t>
+          <t>{'var_smoothing': 1e-11, 'priors': None}</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>NaiveBayes</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.07150053977966309</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.9804441893856517</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.987012987012987</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.986977845425334</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.9863175675675676</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>{'var_smoothing': 1e-11, 'priors': None}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_NaiveBayes_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_NaiveBayes_kmeans_classification.xlsx
@@ -491,7 +491,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.05242013931274414</v>
+        <v>0.04969406127929688</v>
       </c>
       <c r="E2" t="n">
         <v>0.9804397703729418</v>
@@ -526,7 +526,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.04877781867980957</v>
+        <v>0.04880928993225098</v>
       </c>
       <c r="E3" t="n">
         <v>0.9804280526546304</v>
@@ -561,7 +561,7 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>0.07150053977966309</v>
+        <v>0.08411765098571777</v>
       </c>
       <c r="E4" t="n">
         <v>0.9804441893856517</v>
@@ -657,7 +657,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.05242013931274414</v>
+        <v>0.04969406127929688</v>
       </c>
       <c r="E2" t="n">
         <v>0.9804397703729418</v>
@@ -692,7 +692,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.04877781867980957</v>
+        <v>0.04880928993225098</v>
       </c>
       <c r="E3" t="n">
         <v>0.9804280526546304</v>
@@ -727,7 +727,7 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>0.07150053977966309</v>
+        <v>0.08411765098571777</v>
       </c>
       <c r="E4" t="n">
         <v>0.9804441893856517</v>

--- a/output/reports/cv_experiment_NaiveBayes_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_NaiveBayes_kmeans_classification.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -488,22 +488,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D2" t="n">
-        <v>0.04969406127929688</v>
+        <v>0.3184258937835693</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9804397703729418</v>
+        <v>0.7865159669517574</v>
       </c>
       <c r="F2" t="n">
-        <v>0.987012987012987</v>
+        <v>0.8054054054054054</v>
       </c>
       <c r="G2" t="n">
-        <v>0.986977845425334</v>
+        <v>0.7834761366055069</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9863175675675676</v>
+        <v>0.8639571785088667</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -523,59 +523,24 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D3" t="n">
-        <v>0.04880928993225098</v>
+        <v>0.4198737144470215</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9804280526546304</v>
+        <v>0.7869286649232033</v>
       </c>
       <c r="F3" t="n">
-        <v>0.987012987012987</v>
+        <v>0.8054054054054054</v>
       </c>
       <c r="G3" t="n">
-        <v>0.986977845425334</v>
+        <v>0.7834761366055069</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9863175675675676</v>
+        <v>0.8639571785088667</v>
       </c>
       <c r="I3" t="inlineStr">
-        <is>
-          <t>{'var_smoothing': 1e-11, 'priors': None}</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Classification</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>NaiveBayes</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>10</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0.08411765098571777</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.9804441893856517</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.987012987012987</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0.986977845425334</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.9863175675675676</v>
-      </c>
-      <c r="I4" t="inlineStr">
         <is>
           <t>{'var_smoothing': 1e-11, 'priors': None}</t>
         </is>
@@ -592,7 +557,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -654,22 +619,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D2" t="n">
-        <v>0.04969406127929688</v>
+        <v>0.3184258937835693</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9804397703729418</v>
+        <v>0.7865159669517574</v>
       </c>
       <c r="F2" t="n">
-        <v>0.987012987012987</v>
+        <v>0.8054054054054054</v>
       </c>
       <c r="G2" t="n">
-        <v>0.986977845425334</v>
+        <v>0.7834761366055069</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9863175675675676</v>
+        <v>0.8639571785088667</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -689,59 +654,24 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D3" t="n">
-        <v>0.04880928993225098</v>
+        <v>0.4198737144470215</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9804280526546304</v>
+        <v>0.7869286649232033</v>
       </c>
       <c r="F3" t="n">
-        <v>0.987012987012987</v>
+        <v>0.8054054054054054</v>
       </c>
       <c r="G3" t="n">
-        <v>0.986977845425334</v>
+        <v>0.7834761366055069</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9863175675675676</v>
+        <v>0.8639571785088667</v>
       </c>
       <c r="I3" t="inlineStr">
-        <is>
-          <t>{'var_smoothing': 1e-11, 'priors': None}</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Classification</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>NaiveBayes</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>10</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0.08411765098571777</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.9804441893856517</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.987012987012987</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0.986977845425334</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.9863175675675676</v>
-      </c>
-      <c r="I4" t="inlineStr">
         <is>
           <t>{'var_smoothing': 1e-11, 'priors': None}</t>
         </is>

--- a/output/reports/cv_experiment_NaiveBayes_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_NaiveBayes_kmeans_classification.xlsx
@@ -488,26 +488,26 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.3184258937835693</v>
+        <v>0.3644006252288818</v>
       </c>
       <c r="E2" t="n">
-        <v>0.7865159669517574</v>
+        <v>0.7986222110648104</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8054054054054054</v>
+        <v>0.8060155457924975</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7834761366055069</v>
+        <v>0.7984304915439394</v>
       </c>
       <c r="H2" t="n">
-        <v>0.8639571785088667</v>
+        <v>0.9849637004164317</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'var_smoothing': 1e-11, 'priors': None}</t>
+          <t>{'var_smoothing': 0.0001, 'priors': None}</t>
         </is>
       </c>
     </row>
@@ -523,26 +523,26 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.4198737144470215</v>
+        <v>0.6107172966003418</v>
       </c>
       <c r="E3" t="n">
-        <v>0.7869286649232033</v>
+        <v>0.7986221448254553</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8054054054054054</v>
+        <v>0.8060155457924975</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7834761366055069</v>
+        <v>0.7984304915439394</v>
       </c>
       <c r="H3" t="n">
-        <v>0.8639571785088667</v>
+        <v>0.9849637004164317</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'var_smoothing': 1e-11, 'priors': None}</t>
+          <t>{'var_smoothing': 0.0001, 'priors': None}</t>
         </is>
       </c>
     </row>
@@ -619,26 +619,26 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.3184258937835693</v>
+        <v>0.3644006252288818</v>
       </c>
       <c r="E2" t="n">
-        <v>0.7865159669517574</v>
+        <v>0.7986222110648104</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8054054054054054</v>
+        <v>0.8060155457924975</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7834761366055069</v>
+        <v>0.7984304915439394</v>
       </c>
       <c r="H2" t="n">
-        <v>0.8639571785088667</v>
+        <v>0.9849637004164317</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'var_smoothing': 1e-11, 'priors': None}</t>
+          <t>{'var_smoothing': 0.0001, 'priors': None}</t>
         </is>
       </c>
     </row>
@@ -654,26 +654,26 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.4198737144470215</v>
+        <v>0.6107172966003418</v>
       </c>
       <c r="E3" t="n">
-        <v>0.7869286649232033</v>
+        <v>0.7986221448254553</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8054054054054054</v>
+        <v>0.8060155457924975</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7834761366055069</v>
+        <v>0.7984304915439394</v>
       </c>
       <c r="H3" t="n">
-        <v>0.8639571785088667</v>
+        <v>0.9849637004164317</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'var_smoothing': 1e-11, 'priors': None}</t>
+          <t>{'var_smoothing': 0.0001, 'priors': None}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_NaiveBayes_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_NaiveBayes_kmeans_classification.xlsx
@@ -491,7 +491,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.3644006252288818</v>
+        <v>0.3330526351928711</v>
       </c>
       <c r="E2" t="n">
         <v>0.7986222110648104</v>
@@ -526,7 +526,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.6107172966003418</v>
+        <v>0.3865957260131836</v>
       </c>
       <c r="E3" t="n">
         <v>0.7986221448254553</v>
@@ -622,7 +622,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.3644006252288818</v>
+        <v>0.3330526351928711</v>
       </c>
       <c r="E2" t="n">
         <v>0.7986222110648104</v>
@@ -657,7 +657,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.6107172966003418</v>
+        <v>0.3865957260131836</v>
       </c>
       <c r="E3" t="n">
         <v>0.7986221448254553</v>
